--- a/ExcelTool/LubanTools/DataTables/Datas/QuestStoryCondData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/QuestStoryCondData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8533D3-BC3F-4B6F-A86F-A9B00AAF4FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1203AC-043B-4150-9310-21464061B1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -85,18 +85,6 @@
   </si>
   <si>
     <t>游戏评分（暂不实现）</t>
-  </si>
-  <si>
-    <t>条件1</t>
-  </si>
-  <si>
-    <t>100001+1/20001+2</t>
-  </si>
-  <si>
-    <t>10100+10101</t>
-  </si>
-  <si>
-    <t>条件2</t>
   </si>
   <si>
     <t>string</t>
@@ -157,18 +145,67 @@
     <t>前置完成任务</t>
   </si>
   <si>
-    <t>10001+Goodwill+10/10002+Goodwill+10</t>
+    <t>测试条件-多项AND(道具+好感+对话+天数)</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
-    <t>2</t>
+    <t>100001+1</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
+    <t>10001+Goodwill+10</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>10100+10101</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
     <t>All</t>
-  </si>
-  <si>
-    <t>0</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试条件-无门槛(空)</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试条件-道具持有</t>
+  </si>
+  <si>
+    <t>100001+1</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>测试条件-NPC好感</t>
+  </si>
+  <si>
+    <t>10001+Goodwill+10</t>
+  </si>
+  <si>
+    <t>测试条件-对话前置</t>
+  </si>
+  <si>
+    <t>10100</t>
+  </si>
+  <si>
+    <t>测试条件-天数达到第2天</t>
+  </si>
+  <si>
+    <t>测试条件-时间段黄昏</t>
+  </si>
+  <si>
+    <t>Evening</t>
+  </si>
+  <si>
+    <t>测试条件-前置任务10001完成</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>测试条件-剧情前置(尚未实现,永不满足)</t>
   </si>
 </sst>
 </file>
@@ -178,9 +215,9 @@
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="184" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="185" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="186" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -855,7 +892,7 @@
     <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -864,7 +901,7 @@
     <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1005,7 +1042,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1385,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9" style="2" customWidth="1"/>
@@ -1416,7 +1453,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1425,13 +1462,13 @@
         <v>5</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>6</v>
@@ -1451,37 +1488,37 @@
         <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1495,10 +1532,10 @@
         <v>13</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>14</v>
@@ -1507,13 +1544,13 @@
         <v>15</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>16</v>
@@ -1529,42 +1566,42 @@
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
+      <c r="C4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
+      <c r="C5" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="5" t="s">
-        <v>42</v>
+      <c r="H5" s="5">
+        <v>0</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -1655,7 +1692,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -1663,13 +1700,126 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>10003</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>10004</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>10005</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>10006</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>10007</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>10008</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>10009</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
